--- a/artfynd/A 21248-2025 artfynd.xlsx
+++ b/artfynd/A 21248-2025 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>127404211</v>
       </c>
       <c r="B2" t="n">
-        <v>79014</v>
+        <v>79018</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -775,7 +775,7 @@
         <v>127404188</v>
       </c>
       <c r="B3" t="n">
-        <v>91291</v>
+        <v>91295</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -872,7 +872,7 @@
         <v>127404006</v>
       </c>
       <c r="B4" t="n">
-        <v>57657</v>
+        <v>57661</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>

--- a/artfynd/A 21248-2025 artfynd.xlsx
+++ b/artfynd/A 21248-2025 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>127404211</v>
       </c>
       <c r="B2" t="n">
-        <v>79018</v>
+        <v>79020</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -775,7 +775,7 @@
         <v>127404188</v>
       </c>
       <c r="B3" t="n">
-        <v>91295</v>
+        <v>91297</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -872,7 +872,7 @@
         <v>127404006</v>
       </c>
       <c r="B4" t="n">
-        <v>57661</v>
+        <v>57663</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>

--- a/artfynd/A 21248-2025 artfynd.xlsx
+++ b/artfynd/A 21248-2025 artfynd.xlsx
@@ -775,7 +775,7 @@
         <v>127404188</v>
       </c>
       <c r="B3" t="n">
-        <v>91297</v>
+        <v>91303</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>

--- a/artfynd/A 21248-2025 artfynd.xlsx
+++ b/artfynd/A 21248-2025 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>127404211</v>
       </c>
       <c r="B2" t="n">
-        <v>79020</v>
+        <v>79023</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -775,7 +775,7 @@
         <v>127404188</v>
       </c>
       <c r="B3" t="n">
-        <v>91303</v>
+        <v>91306</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -872,7 +872,7 @@
         <v>127404006</v>
       </c>
       <c r="B4" t="n">
-        <v>57663</v>
+        <v>57666</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>

--- a/artfynd/A 21248-2025 artfynd.xlsx
+++ b/artfynd/A 21248-2025 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>127404211</v>
       </c>
       <c r="B2" t="n">
-        <v>79023</v>
+        <v>79029</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -775,7 +775,7 @@
         <v>127404188</v>
       </c>
       <c r="B3" t="n">
-        <v>91306</v>
+        <v>91314</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -872,7 +872,7 @@
         <v>127404006</v>
       </c>
       <c r="B4" t="n">
-        <v>57666</v>
+        <v>57672</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>

--- a/artfynd/A 21248-2025 artfynd.xlsx
+++ b/artfynd/A 21248-2025 artfynd.xlsx
@@ -775,7 +775,7 @@
         <v>127404188</v>
       </c>
       <c r="B3" t="n">
-        <v>91314</v>
+        <v>91315</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>

--- a/artfynd/A 21248-2025 artfynd.xlsx
+++ b/artfynd/A 21248-2025 artfynd.xlsx
@@ -775,7 +775,7 @@
         <v>127404188</v>
       </c>
       <c r="B3" t="n">
-        <v>91315</v>
+        <v>91316</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>

--- a/artfynd/A 21248-2025 artfynd.xlsx
+++ b/artfynd/A 21248-2025 artfynd.xlsx
@@ -775,7 +775,7 @@
         <v>127404188</v>
       </c>
       <c r="B3" t="n">
-        <v>91316</v>
+        <v>91317</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>

--- a/artfynd/A 21248-2025 artfynd.xlsx
+++ b/artfynd/A 21248-2025 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY4"/>
+  <dimension ref="A1:AY5"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -675,32 +675,32 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>127404211</v>
+        <v>127404188</v>
       </c>
       <c r="B2" t="n">
-        <v>79029</v>
+        <v>91872</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E2" t="n">
-        <v>6425</v>
+        <v>5447</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Vedticka</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Fuscoporia viticola</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Schwein.) Murrill</t>
         </is>
       </c>
       <c r="I2" t="inlineStr"/>
@@ -710,10 +710,10 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>591643</v>
+        <v>591641</v>
       </c>
       <c r="R2" t="n">
-        <v>6984798</v>
+        <v>6984795</v>
       </c>
       <c r="S2" t="n">
         <v>15</v>
@@ -772,32 +772,32 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>127404188</v>
+        <v>127404211</v>
       </c>
       <c r="B3" t="n">
-        <v>91317</v>
+        <v>79327</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E3" t="n">
-        <v>5447</v>
+        <v>6425</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Vedticka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Fuscoporia viticola</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(Schwein.) Murrill</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
@@ -807,10 +807,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>591641</v>
+        <v>591643</v>
       </c>
       <c r="R3" t="n">
-        <v>6984795</v>
+        <v>6984798</v>
       </c>
       <c r="S3" t="n">
         <v>15</v>
@@ -872,7 +872,7 @@
         <v>127404006</v>
       </c>
       <c r="B4" t="n">
-        <v>57672</v>
+        <v>57953</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -973,6 +973,103 @@
         </is>
       </c>
       <c r="AY4" t="inlineStr"/>
+    </row>
+    <row r="5">
+      <c r="A5" t="n">
+        <v>105011907</v>
+      </c>
+      <c r="B5" t="n">
+        <v>79327</v>
+      </c>
+      <c r="D5" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E5" t="n">
+        <v>6425</v>
+      </c>
+      <c r="F5" t="inlineStr">
+        <is>
+          <t>Garnlav</t>
+        </is>
+      </c>
+      <c r="G5" t="inlineStr">
+        <is>
+          <t>Alectoria sarmentosa</t>
+        </is>
+      </c>
+      <c r="H5" t="inlineStr">
+        <is>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I5" t="inlineStr"/>
+      <c r="P5" t="inlineStr">
+        <is>
+          <t>Ödingen, Jmt</t>
+        </is>
+      </c>
+      <c r="Q5" t="n">
+        <v>591509</v>
+      </c>
+      <c r="R5" t="n">
+        <v>6985046</v>
+      </c>
+      <c r="S5" t="n">
+        <v>15</v>
+      </c>
+      <c r="T5" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U5" t="inlineStr">
+        <is>
+          <t>Ragunda</t>
+        </is>
+      </c>
+      <c r="V5" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="W5" t="inlineStr">
+        <is>
+          <t>Fors</t>
+        </is>
+      </c>
+      <c r="Y5" t="inlineStr">
+        <is>
+          <t>2022-12-10</t>
+        </is>
+      </c>
+      <c r="AA5" t="inlineStr">
+        <is>
+          <t>2022-12-10</t>
+        </is>
+      </c>
+      <c r="AD5" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE5" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG5" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT5" t="inlineStr"/>
+      <c r="AW5" t="inlineStr">
+        <is>
+          <t>Maria Danvind</t>
+        </is>
+      </c>
+      <c r="AX5" t="inlineStr">
+        <is>
+          <t>Maria Danvind</t>
+        </is>
+      </c>
+      <c r="AY5" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/artfynd/A 21248-2025 artfynd.xlsx
+++ b/artfynd/A 21248-2025 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY5"/>
+  <dimension ref="A1:AZ5"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -672,6 +672,11 @@
           <t>Projektnamn</t>
         </is>
       </c>
+      <c r="AZ1" t="inlineStr">
+        <is>
+          <t>Artportalenlänk</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="n">
@@ -769,6 +774,11 @@
         </is>
       </c>
       <c r="AY2" t="inlineStr"/>
+      <c r="AZ2" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/127404188</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="n">
@@ -866,6 +876,11 @@
         </is>
       </c>
       <c r="AY3" t="inlineStr"/>
+      <c r="AZ3" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/105011907</t>
+        </is>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="n">
@@ -963,6 +978,11 @@
         </is>
       </c>
       <c r="AY4" t="inlineStr"/>
+      <c r="AZ4" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/127404211</t>
+        </is>
+      </c>
     </row>
     <row r="5">
       <c r="A5" t="n">
@@ -1070,8 +1090,19 @@
         </is>
       </c>
       <c r="AY5" t="inlineStr"/>
+      <c r="AZ5" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/127404006</t>
+        </is>
+      </c>
     </row>
   </sheetData>
+  <hyperlinks>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ2" r:id="rId1"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ3" r:id="rId2"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ4" r:id="rId3"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ5" r:id="rId4"/>
+  </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>